--- a/results/0916-all/浙闽丘陵山地林农区/tech_selected_summary.xlsx
+++ b/results/0916-all/浙闽丘陵山地林农区/tech_selected_summary.xlsx
@@ -262,202 +262,202 @@
     <t>周宁县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 3512.46</t>
+    <t>3512.46</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -511,7 +511,7 @@
     <t>4R(Right rate)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 47089017.05</t>
+    <t>47089017.05</t>
   </si>
   <si>
     <t>Biochar_sheep &amp; goat</t>
@@ -550,7 +550,7 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 77178410.76</t>
+    <t>77178410.76</t>
   </si>
   <si>
     <t>Yucca extract_Beef cattle</t>
@@ -580,10 +580,10 @@
     <t>4R(Right rate)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 97665967.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>97665967.31</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>EEF(CRF)_vegetable</t>
@@ -592,7 +592,7 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 78760256.90</t>
+    <t>78760256.90</t>
   </si>
   <si>
     <t>Increasing byproduct_beef cattle</t>
@@ -619,7 +619,7 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 81408827.99</t>
+    <t>81408827.99</t>
   </si>
   <si>
     <t>compost（low）≤30%_wheat</t>
@@ -628,7 +628,7 @@
     <t>EEF(NI)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 59653703.40</t>
+    <t>59653703.40</t>
   </si>
   <si>
     <t>Low protein diet_Pig</t>
@@ -751,16 +751,16 @@
     <t>irrigation (water-saving irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 2810386591.05</t>
-  </si>
-  <si>
-    <t>总经济成本: 1475563.47</t>
-  </si>
-  <si>
-    <t>总经济成本: 214343399.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 283656010.37</t>
+    <t>2810386591.05</t>
+  </si>
+  <si>
+    <t>1475563.47</t>
+  </si>
+  <si>
+    <t>214343399.85</t>
+  </si>
+  <si>
+    <t>283656010.37</t>
   </si>
   <si>
     <t>Yucca extract_Poultry</t>
@@ -775,19 +775,19 @@
     <t>Cover_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 134396458.63</t>
+    <t>134396458.63</t>
   </si>
   <si>
     <t>Yucca extract_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 16107150.83</t>
-  </si>
-  <si>
-    <t>总经济成本: 8959181.98</t>
-  </si>
-  <si>
-    <t>总经济成本: 113222719.22</t>
+    <t>16107150.83</t>
+  </si>
+  <si>
+    <t>8959181.98</t>
+  </si>
+  <si>
+    <t>113222719.22</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
@@ -796,16 +796,16 @@
     <t>Acidification_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 149235155.90</t>
+    <t>149235155.90</t>
   </si>
   <si>
     <t>4R(Right rate)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 192534056.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 1177809.24</t>
+    <t>192534056.03</t>
+  </si>
+  <si>
+    <t>1177809.24</t>
   </si>
   <si>
     <t>Frequent removal_sheep&amp;goat</t>
@@ -823,19 +823,19 @@
     <t>band application_pig</t>
   </si>
   <si>
-    <t>总经济成本: 633424783.28</t>
-  </si>
-  <si>
-    <t>总经济成本: 28360811.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 149223178.73</t>
-  </si>
-  <si>
-    <t>总经济成本: 57376916.22</t>
-  </si>
-  <si>
-    <t>总经济成本: 28249661.37</t>
+    <t>633424783.28</t>
+  </si>
+  <si>
+    <t>28360811.84</t>
+  </si>
+  <si>
+    <t>149223178.73</t>
+  </si>
+  <si>
+    <t>57376916.22</t>
+  </si>
+  <si>
+    <t>28249661.37</t>
   </si>
   <si>
     <t>By-products source_beef cattle</t>
@@ -844,10 +844,10 @@
     <t>4R(Right time)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 36511563.26</t>
-  </si>
-  <si>
-    <t>总经济成本: 58569361.32</t>
+    <t>36511563.26</t>
+  </si>
+  <si>
+    <t>58569361.32</t>
   </si>
   <si>
     <t>surface crust cover_dairy</t>
@@ -862,7 +862,7 @@
     <t>tillage management (zero tillage)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 97827396.36</t>
+    <t>97827396.36</t>
   </si>
   <si>
     <t>Low protein diet_dairy</t>
@@ -883,67 +883,67 @@
     <t>incorporation_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 31855554.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 566721683.39</t>
+    <t>31855554.60</t>
+  </si>
+  <si>
+    <t>566721683.39</t>
   </si>
   <si>
     <t>surface crust cover_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 23539972.79</t>
-  </si>
-  <si>
-    <t>总经济成本: 87950188.57</t>
-  </si>
-  <si>
-    <t>总经济成本: 594939.19</t>
-  </si>
-  <si>
-    <t>总经济成本: 53735652.32</t>
+    <t>23539972.79</t>
+  </si>
+  <si>
+    <t>87950188.57</t>
+  </si>
+  <si>
+    <t>594939.19</t>
+  </si>
+  <si>
+    <t>53735652.32</t>
   </si>
   <si>
     <t>Urease Inhibitor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 360775818.83</t>
-  </si>
-  <si>
-    <t>总经济成本: 100219320.51</t>
-  </si>
-  <si>
-    <t>总经济成本: 147891551.66</t>
-  </si>
-  <si>
-    <t>总经济成本: 29489487.81</t>
+    <t>360775818.83</t>
+  </si>
+  <si>
+    <t>100219320.51</t>
+  </si>
+  <si>
+    <t>147891551.66</t>
+  </si>
+  <si>
+    <t>29489487.81</t>
   </si>
   <si>
     <t>cover crop (non-leguminous)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 76849031.30</t>
-  </si>
-  <si>
-    <t>总经济成本: 13462037.50</t>
+    <t>76849031.30</t>
+  </si>
+  <si>
+    <t>13462037.50</t>
   </si>
   <si>
     <t>Screw press_pig</t>
   </si>
   <si>
-    <t>总经济成本: 41398574.08</t>
-  </si>
-  <si>
-    <t>总经济成本: 33002382.48</t>
+    <t>41398574.08</t>
+  </si>
+  <si>
+    <t>33002382.48</t>
   </si>
   <si>
     <t>EEF(DI)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 138645998.09</t>
-  </si>
-  <si>
-    <t>总经济成本: 18959740.58</t>
+    <t>138645998.09</t>
+  </si>
+  <si>
+    <t>18959740.58</t>
   </si>
   <si>
     <t>Frequent removal_dairy</t>
@@ -955,16 +955,16 @@
     <t>Chemical amendments_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 290208933.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 61932075.65</t>
-  </si>
-  <si>
-    <t>总经济成本: 39346734.68</t>
-  </si>
-  <si>
-    <t>总经济成本: 68977430.14</t>
+    <t>290208933.35</t>
+  </si>
+  <si>
+    <t>61932075.65</t>
+  </si>
+  <si>
+    <t>39346734.68</t>
+  </si>
+  <si>
+    <t>68977430.14</t>
   </si>
   <si>
     <t>manure（high）≥70%_rice</t>
@@ -973,10 +973,10 @@
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 79226592.45</t>
-  </si>
-  <si>
-    <t>总经济成本: 13569017.33</t>
+    <t>79226592.45</t>
+  </si>
+  <si>
+    <t>13569017.33</t>
   </si>
   <si>
     <t>surface applied  plus irrigation _sheep&amp;goat</t>
@@ -985,13 +985,13 @@
     <t>EEF(DI)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 414026034.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 66264171.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 319363359.36</t>
+    <t>414026034.75</t>
+  </si>
+  <si>
+    <t>66264171.50</t>
+  </si>
+  <si>
+    <t>319363359.36</t>
   </si>
   <si>
     <t>EEF(CRF)_wheat</t>
@@ -1000,37 +1000,37 @@
     <t>4R(Right place)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 85667934.64</t>
-  </si>
-  <si>
-    <t>总经济成本: 60438491.82</t>
-  </si>
-  <si>
-    <t>总经济成本: 87761814.05</t>
-  </si>
-  <si>
-    <t>总经济成本: 68172237.77</t>
+    <t>85667934.64</t>
+  </si>
+  <si>
+    <t>60438491.82</t>
+  </si>
+  <si>
+    <t>87761814.05</t>
+  </si>
+  <si>
+    <t>68172237.77</t>
   </si>
   <si>
     <t>rolller press_pig</t>
   </si>
   <si>
-    <t>总经济成本: 111144216.29</t>
-  </si>
-  <si>
-    <t>总经济成本: 212775991.23</t>
-  </si>
-  <si>
-    <t>总经济成本: 17517592.12</t>
-  </si>
-  <si>
-    <t>总经济成本: 148587753.35</t>
+    <t>111144216.29</t>
+  </si>
+  <si>
+    <t>212775991.23</t>
+  </si>
+  <si>
+    <t>17517592.12</t>
+  </si>
+  <si>
+    <t>148587753.35</t>
   </si>
   <si>
     <t>Algae_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 3376270.45</t>
+    <t>3376270.45</t>
   </si>
 </sst>
 </file>
